--- a/artfynd/A 47850-2022 artfynd.xlsx
+++ b/artfynd/A 47850-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47850-2022 artfynd.xlsx
+++ b/artfynd/A 47850-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106032812</v>
+        <v>106032802</v>
       </c>
       <c r="B2" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1049</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595332.2385764377</v>
+        <v>595426</v>
       </c>
       <c r="R2" t="n">
-        <v>6669912.204573136</v>
+        <v>6669692</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -789,7 +774,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Gammal högstubbe av tall # Pinus sylvestris</t>
+          <t>Tallåga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,15 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106032802</v>
+        <v>106032815</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,34 +803,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jon-Olsmossen, Botebo, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595425.7710847252</v>
+        <v>595333</v>
       </c>
       <c r="R3" t="n">
-        <v>6669692.475679609</v>
+        <v>6669964</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,21 +869,11 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -906,22 +885,22 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Äldre barrblandskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Tallåga # Pinus sylvestris</t>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,37 +918,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106032819</v>
+        <v>106032805</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92640</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>757</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -988,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595552.3196965416</v>
+        <v>595209</v>
       </c>
       <c r="R4" t="n">
-        <v>6669833.753339244</v>
+        <v>6669935</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,19 +995,14 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ej mikroskoperad</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,27 +1011,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre barrblandskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>På senvuxen klen granlåga # Picea abies</t>
+          <t>Tallåga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1080,59 +1050,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106032797</v>
+        <v>106032812</v>
       </c>
       <c r="B5" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Jon-Olsmossen, Botebo, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595380.6158428271</v>
+        <v>595332</v>
       </c>
       <c r="R5" t="n">
-        <v>6669874.610426888</v>
+        <v>6669912</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1162,21 +1118,11 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1185,6 +1131,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Gammal högstubbe av tall # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1201,15 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106032821</v>
+        <v>106032808</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,43 +1178,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Jon-Olsmossen, Botebo, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595577.3021937197</v>
+        <v>595274</v>
       </c>
       <c r="R6" t="n">
-        <v>6669832.412109513</v>
+        <v>6669925</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1283,21 +1235,11 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1309,22 +1251,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Äldre barrblandskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1342,15 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106032806</v>
+        <v>106032813</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,34 +1280,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Jon-Olsmossen, Botebo, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595304.298625942</v>
+        <v>595328</v>
       </c>
       <c r="R7" t="n">
-        <v>6669969.756086072</v>
+        <v>6669898</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1415,21 +1346,11 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1446,17 +1367,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>På stam av gammal tall # Pinus sylvestris</t>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1474,37 +1395,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106032807</v>
+        <v>106032816</v>
       </c>
       <c r="B8" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1523,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595304.298625942</v>
+        <v>595333</v>
       </c>
       <c r="R8" t="n">
-        <v>6669969.756086072</v>
+        <v>6669964</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1556,19 +1472,9 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1615,37 +1521,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106032803</v>
+        <v>106032817</v>
       </c>
       <c r="B9" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1664,10 +1565,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595408.6167022884</v>
+        <v>595350</v>
       </c>
       <c r="R9" t="n">
-        <v>6669718.928510376</v>
+        <v>6669950</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1697,21 +1598,11 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1720,6 +1611,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1736,37 +1647,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106032810</v>
+        <v>106032798</v>
       </c>
       <c r="B10" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1776,10 +1682,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595277.1337345131</v>
+        <v>595425</v>
       </c>
       <c r="R10" t="n">
-        <v>6669920.734074925</v>
+        <v>6669778</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1809,21 +1715,11 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1835,7 +1731,22 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Gammal tallåga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1853,37 +1764,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106032813</v>
+        <v>106032797</v>
       </c>
       <c r="B11" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1902,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595328.6122077182</v>
+        <v>595381</v>
       </c>
       <c r="R11" t="n">
-        <v>6669898.163258505</v>
+        <v>6669875</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1935,21 +1841,11 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1958,26 +1854,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1994,37 +1870,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106032816</v>
+        <v>106032799</v>
       </c>
       <c r="B12" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2043,10 +1914,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595332.3881118452</v>
+        <v>595496</v>
       </c>
       <c r="R12" t="n">
-        <v>6669964.011185481</v>
+        <v>6669750</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2076,21 +1947,11 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2099,26 +1960,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2135,15 +1976,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106032820</v>
+        <v>106032803</v>
       </c>
       <c r="B13" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2184,10 +2020,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595546.5123750143</v>
+        <v>595408</v>
       </c>
       <c r="R13" t="n">
-        <v>6669807.699698461</v>
+        <v>6669719</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2217,21 +2053,11 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2240,11 +2066,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Äldre tallskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2261,43 +2082,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106032818</v>
+        <v>106032807</v>
       </c>
       <c r="B14" t="n">
-        <v>5413</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101920</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2306,10 +2126,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595380.2532526108</v>
+        <v>595305</v>
       </c>
       <c r="R14" t="n">
-        <v>6669811.838334966</v>
+        <v>6669970</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2339,53 +2159,38 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ett flertal kläckhål i söderläge på gammal tallåga.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre barrblandskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Tallåga # Pinus sylvestris</t>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2403,37 +2208,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>106032817</v>
+        <v>106032819</v>
       </c>
       <c r="B15" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2452,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595349.7028189165</v>
+        <v>595552</v>
       </c>
       <c r="R15" t="n">
-        <v>6669950.514694593</v>
+        <v>6669834</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2485,21 +2285,11 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2511,7 +2301,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2526,7 +2316,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Granlåga # Picea abies</t>
+          <t>På senvuxen klen granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2544,15 +2334,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>106032800</v>
+        <v>106032820</v>
       </c>
       <c r="B16" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2560,38 +2345,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Jon-Olsmossen, Botebo, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595441.0218874034</v>
+        <v>595546</v>
       </c>
       <c r="R16" t="n">
-        <v>6669662.486180879</v>
+        <v>6669808</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2621,30 +2411,24 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Äldre tallskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2661,37 +2445,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106032799</v>
+        <v>106032811</v>
       </c>
       <c r="B17" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2710,10 +2489,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595496.1216203274</v>
+        <v>595301</v>
       </c>
       <c r="R17" t="n">
-        <v>6669750.098469635</v>
+        <v>6669888</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2743,21 +2522,11 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2766,6 +2535,11 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2782,37 +2556,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>106032808</v>
+        <v>106032806</v>
       </c>
       <c r="B18" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2822,10 +2591,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595274.0127684863</v>
+        <v>595305</v>
       </c>
       <c r="R18" t="n">
-        <v>6669925.634007336</v>
+        <v>6669970</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2855,21 +2624,11 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2882,6 +2641,21 @@
       <c r="AI18" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>På stam av gammal tall # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2899,50 +2673,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>106032798</v>
+        <v>106032821</v>
       </c>
       <c r="B19" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jon-Olsmossen, Botebo, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595425.0383253184</v>
+        <v>595577</v>
       </c>
       <c r="R19" t="n">
-        <v>6669778.135188845</v>
+        <v>6669832</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2972,21 +2750,11 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2998,22 +2766,22 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Gammal tallåga # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3031,59 +2799,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>106032815</v>
+        <v>120738194</v>
       </c>
       <c r="B20" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78685</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6443</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Jon-Olsmossen, Botebo, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595332.3881118452</v>
+        <v>595411</v>
       </c>
       <c r="R20" t="n">
-        <v>6669964.011185481</v>
+        <v>6669721</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3110,22 +2864,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3139,22 +2883,22 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Granlåga # Picea abies</t>
+          <t>På grov gammal tallåga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3172,15 +2916,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>106032811</v>
+        <v>120738195</v>
       </c>
       <c r="B21" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3188,43 +2927,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Jon-Olsmossen, Botebo, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595300.437718006</v>
+        <v>595456</v>
       </c>
       <c r="R21" t="n">
-        <v>6669887.966637347</v>
+        <v>6669708</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3251,22 +2981,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3280,7 +3000,22 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog</t>
+          <t>Äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3298,15 +3033,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>106032805</v>
+        <v>106032801</v>
       </c>
       <c r="B22" t="n">
-        <v>90082</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3314,38 +3044,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>757</v>
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Jon-Olsmossen, Botebo, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595208.9104826588</v>
+        <v>595419</v>
       </c>
       <c r="R22" t="n">
-        <v>6669934.900869153</v>
+        <v>6669685</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3375,55 +3101,19 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ej mikroskoperad</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Tallåga # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3440,62 +3130,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>106032804</v>
+        <v>106032810</v>
       </c>
       <c r="B23" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Jon-Olsmossen, Botebo, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595278.0194212182</v>
+        <v>595277</v>
       </c>
       <c r="R23" t="n">
-        <v>6669867.459472805</v>
+        <v>6669920</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3525,28 +3198,17 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3570,50 +3232,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>106032801</v>
+        <v>106032818</v>
       </c>
       <c r="B24" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>101920</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Jon-Olsmossen, Botebo, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595418.9716405865</v>
+        <v>595380</v>
       </c>
       <c r="R24" t="n">
-        <v>6669685.324778596</v>
+        <v>6669812</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3643,29 +3305,44 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ett flertal kläckhål i söderläge på gammal tallåga.</t>
         </is>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Tallåga # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3682,50 +3359,58 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120738194</v>
+        <v>120744309</v>
       </c>
       <c r="B25" t="n">
-        <v>77936</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5482</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6443</v>
+        <v>101920</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jon-Olsmossen, Botebo, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595411</v>
+        <v>595352</v>
       </c>
       <c r="R25" t="n">
-        <v>6669721</v>
+        <v>6669816</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3752,12 +3437,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre kläckhål på en gammal liggande tallstam i söderläge</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3766,28 +3456,9 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Äldre tallskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>På grov gammal tallåga # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3804,50 +3475,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120738195</v>
+        <v>106032800</v>
       </c>
       <c r="B26" t="n">
-        <v>78332</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jon-Olsmossen, Botebo, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595456</v>
+        <v>595441</v>
       </c>
       <c r="R26" t="n">
-        <v>6669708</v>
+        <v>6669663</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3874,12 +3544,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3888,28 +3558,9 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Äldre tallskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Kolad tallstubbe # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3926,63 +3577,57 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120744309</v>
+        <v>106032804</v>
       </c>
       <c r="B27" t="n">
-        <v>5472</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101920</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jon-Olsmossen, Botebo, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595352</v>
+        <v>595278</v>
       </c>
       <c r="R27" t="n">
-        <v>6669816</v>
+        <v>6669868</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4017,11 +3662,6 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre kläckhål på en gammal liggande tallstam i söderläge</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4031,6 +3671,11 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">

--- a/artfynd/A 47850-2022 artfynd.xlsx
+++ b/artfynd/A 47850-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032802</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032815</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032805</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1164,6 +1184,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032812</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1266,6 +1291,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032808</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1392,6 +1422,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032813</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1518,6 +1553,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032816</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1644,6 +1684,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032817</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1761,6 +1806,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032798</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1867,6 +1917,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032797</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1973,6 +2028,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032799</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2079,6 +2139,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032803</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2205,6 +2270,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032807</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2331,6 +2401,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032819</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2442,6 +2517,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032820</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2553,6 +2633,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032811</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2670,6 +2755,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032806</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2796,6 +2886,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032821</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2913,6 +3008,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120738194</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3030,6 +3130,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120738195</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3127,6 +3232,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032801</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3229,6 +3339,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032810</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3356,6 +3471,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032818</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3472,6 +3592,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120744309</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3574,6 +3699,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032800</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3689,8 +3819,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032804</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>